--- a/output/2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,6 @@
           <t>+385 1 3387 206</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Rivenditore/installatore sistemi ventilazione, ventilatori, griglie, diffusori, recuperatori di calore. Email generica non reperibile in fonti pubbliche. Confermata da fininfo.hr, emajstor.hr, D&amp;B.</t>
@@ -712,7 +711,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -754,7 +753,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -796,7 +795,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -838,7 +837,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
